--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_hr_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_hr_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-09-2021 08:30</t>
+          <t>2021-09-17 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>27-12-2021 08:30</t>
+          <t>2021-12-27 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>30-06-2021 08:30</t>
+          <t>2021-06-30 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>14-03-2021 08:30</t>
+          <t>2021-03-14 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>26-12-2021 08:30</t>
+          <t>2021-12-26 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>26-12-2021 08:30</t>
+          <t>2021-12-26 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>26-12-2021 08:30</t>
+          <t>2021-12-26 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13418,7 +13418,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>19-08-2021 08:30</t>
+          <t>2021-08-19 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>11-12-2021 08:30</t>
+          <t>2021-11-12 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>19-08-2021 08:30</t>
+          <t>2021-08-19 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>11-12-2021 08:30</t>
+          <t>2021-11-12 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17147,7 +17147,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -18093,7 +18093,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>24-11-2021 08:30</t>
+          <t>2021-11-24 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18378,7 +18378,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>25-12-2021 08:30</t>
+          <t>2021-12-25 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -19031,7 +19031,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19682,7 +19682,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
